--- a/public/docs/datas/words.xlsx
+++ b/public/docs/datas/words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF555068-9679-476D-B236-352717F62F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE5146B-74A3-4222-858B-B5932C49178C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31185" yWindow="7305" windowWidth="20340" windowHeight="13005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,46 +66,46 @@
     <t>人造的；人工的；虚假的</t>
   </si>
   <si>
-    <t>雅思/GRE/商务高频</t>
-  </si>
-  <si>
     <t>ranges</t>
   </si>
   <si>
-    <t>artifice/artificiality</t>
-  </si>
-  <si>
     <t>The artificial flowers looked almost real.→这些人造花看起来几乎像真的一样。</t>
   </si>
   <si>
-    <t>artificial intelligence→人工智能/artificial light→人造光</t>
-  </si>
-  <si>
     <t>intelligence</t>
   </si>
   <si>
     <t>来自拉丁语 'intelligere'，由 'inter'（在……之间）+ 'legere'（选择，阅读）构成，引申为“理解力，智力”。</t>
   </si>
   <si>
-    <t>intellect/intellectual</t>
-  </si>
-  <si>
     <t>n.</t>
   </si>
   <si>
     <t>智力；智能；理解力；情报</t>
   </si>
   <si>
-    <t>考研/雅思/托福高频</t>
-  </si>
-  <si>
     <t>She showed remarkable intelligence in solving the problem.→她在解决问题时表现出非凡的智慧。</t>
   </si>
   <si>
-    <t>artificial intelligence→人工智能/military intelligence→军事情报</t>
-  </si>
-  <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>artifice//artificiality</t>
+  </si>
+  <si>
+    <t>intellect//intellectual</t>
+  </si>
+  <si>
+    <t>artificial intelligence→人工智能//military intelligence→军事情报</t>
+  </si>
+  <si>
+    <t>artificial intelligence→人工智能//artificial light→人造光</t>
+  </si>
+  <si>
+    <t>雅思//GRE//商务</t>
+  </si>
+  <si>
+    <t>考研//雅思//托福</t>
   </si>
 </sst>
 </file>
@@ -475,7 +475,7 @@
         <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>8</v>
@@ -484,7 +484,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
@@ -495,7 +495,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>10</v>
@@ -504,39 +504,39 @@
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs/datas/words.xlsx
+++ b/public/docs/datas/words.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE5146B-74A3-4222-858B-B5932C49178C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{653609E1-6D76-497E-A358-54DE67E0603D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31185" yWindow="7305" windowWidth="20340" windowHeight="13005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5640" yWindow="8016" windowWidth="21600" windowHeight="15936" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="words" sheetId="1" r:id="rId1"/>
+    <sheet name="opts" sheetId="2" r:id="rId2"/>
+    <sheet name="tenses" sheetId="3" r:id="rId3"/>
+    <sheet name="temp" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">words!$A$1:$J$3</definedName>
+    <definedName name="class">opts!$A$2:$A$15</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="196">
   <si>
     <t>word</t>
   </si>
@@ -45,90 +49,777 @@
     <t>related</t>
   </si>
   <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>phrases</t>
+  </si>
+  <si>
+    <t>examples</t>
+  </si>
+  <si>
+    <t>来自拉丁语 'artificialis'，由 'ars'（技巧）+ 'facere'（制造）构成，引申为“人为的，人工的”。</t>
+  </si>
+  <si>
+    <t>adj.</t>
+  </si>
+  <si>
+    <t>人造的；人工的；虚假的</t>
+  </si>
+  <si>
+    <t>ranges</t>
+  </si>
+  <si>
+    <t>The artificial flowers looked almost real.→这些人造花看起来几乎像真的一样。</t>
+  </si>
+  <si>
+    <t>intelligence</t>
+  </si>
+  <si>
+    <t>来自拉丁语 'intelligere'，由 'inter'（在……之间）+ 'legere'（选择，阅读）构成，引申为“理解力，智力”。</t>
+  </si>
+  <si>
+    <t>n.</t>
+  </si>
+  <si>
+    <t>智力；智能；理解力；情报</t>
+  </si>
+  <si>
+    <t>She showed remarkable intelligence in solving the problem.→她在解决问题时表现出非凡的智慧。</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>artifice//artificiality</t>
+  </si>
+  <si>
+    <t>intellect//intellectual</t>
+  </si>
+  <si>
+    <t>artificial intelligence→人工智能//military intelligence→军事情报</t>
+  </si>
+  <si>
+    <t>artificial intelligence→人工智能//artificial light→人造光</t>
+  </si>
+  <si>
+    <t>雅思//GRE//商务</t>
+  </si>
+  <si>
+    <t>考研//雅思//托福</t>
+  </si>
+  <si>
+    <t>revolutionise</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>vt.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>彻底改变；完全变革</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>algorithmic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>算法的；规则系统的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bias</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>偏见；偏心；偏向</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>discrimination</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>区别对待；歧视；偏袒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>destruction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>摧毁；毁灭；破坏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>extinction</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>humanity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>灭绝，绝种，消亡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人；人类</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>observer</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>观察家；观察员；评论员</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dystopian</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>反乌托邦的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>thorny</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>令人苦恼的；棘手的，麻烦的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>radically</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>adv.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重大地，根本地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>accelerate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使加速，加快</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>medicine</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>医学；医疗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>luminary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>专家；权威；有影响的人物；杰出人物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>turbocharge</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>促进，推动，增强</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>n.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>名词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>v.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>动词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>vi.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不及物动词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>及物动词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pron.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>代词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>形容词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>副词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>abbr.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩写符号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>conj.</t>
+  </si>
+  <si>
+    <t>连词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>感叹词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>class</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在完成时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去完成时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将来完成时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去将来完成时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在进行时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去进行时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将来进行时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去将来进行时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在完成进行时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去完成进行时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将来完成进行时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去将来完成进行时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>do</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>did</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>will do</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>would do</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>have done</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>had done</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>will have done</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>would have done</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>is doing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>was doing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>will be doing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>would be doing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>have been doing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>had been doing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>will have been doing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>would have been doing</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>时态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>疑问代词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>介词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冠词</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>num.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>prep.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>art.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>what</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>how old</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>why</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>how many</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>where</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>how much</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>which</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>who</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>whose</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>how</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>how often</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>how soon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>how tall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>how big</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>how long</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>what time</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>when</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>how heavy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>成分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主语</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>谓语</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>宾语</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>表语</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同位语</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>定语</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>状语</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>补足语</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I do my homework.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I will do my homework tomorrow.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I said I would do my homework tomorrow.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I have done my homework.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I will have done my homework tomorrow.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I said I would have done my homework before you open the door.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I am doing my homework now.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I did my homework yesterday.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我做作业。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我会在明天做作业。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我做完作业了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我昨天做作业了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我现在正在做作业。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I was doing my homework when you opened the door.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I had done my homework before you opened the door.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I will be doing my homework at 9:00 tomorrow.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I said I would be doing my homework at 9:00 tomorrow.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>明天九点我会正在做作业。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I have been doing my homework for 3 hours.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我已经做了三个小时的作业了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I had been doing my homework for 3 hours before you opened the door.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在你开门时，我正在做作业。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在你开门前，我已经做了三个小时的作业了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I will have been doing my homework for 3 hours next hour.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>到了下个小时，我就已经做了三个小时的作业了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I said I will have been doing my homework for 3 hours next hour.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我说过，明天九点我会正在做作业。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我说过，我会在你开门前做完作业。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我说过，我会在明天做作业。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在你开门前，我做完作业了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>我说过，到了下个小时，我就已经做了三个小时的作业了。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将来的某个时间点前，已经完成的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去的某个时间点前，已经完成的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>明天我就会做完作业。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在过去的时间说，将来的某个时间点前，已经完成的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去的某段时间，已经完成(一段时间)并且还在持续进行的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将来的某段时间，已经完成(一段时间)并且还在持续进行的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在过去的时间说，将来的某段时间，已经完成(一段时间)并且还在持续进行的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>mean</t>
-  </si>
-  <si>
-    <t>phrases</t>
-  </si>
-  <si>
-    <t>examples</t>
-  </si>
-  <si>
-    <t>来自拉丁语 'artificialis'，由 'ars'（技巧）+ 'facere'（制造）构成，引申为“人为的，人工的”。</t>
-  </si>
-  <si>
-    <t>adj.</t>
-  </si>
-  <si>
-    <t>人造的；人工的；虚假的</t>
-  </si>
-  <si>
-    <t>ranges</t>
-  </si>
-  <si>
-    <t>The artificial flowers looked almost real.→这些人造花看起来几乎像真的一样。</t>
-  </si>
-  <si>
-    <t>intelligence</t>
-  </si>
-  <si>
-    <t>来自拉丁语 'intelligere'，由 'inter'（在……之间）+ 'legere'（选择，阅读）构成，引申为“理解力，智力”。</t>
-  </si>
-  <si>
-    <t>n.</t>
-  </si>
-  <si>
-    <t>智力；智能；理解力；情报</t>
-  </si>
-  <si>
-    <t>She showed remarkable intelligence in solving the problem.→她在解决问题时表现出非凡的智慧。</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>artifice//artificiality</t>
-  </si>
-  <si>
-    <t>intellect//intellectual</t>
-  </si>
-  <si>
-    <t>artificial intelligence→人工智能//military intelligence→军事情报</t>
-  </si>
-  <si>
-    <t>artificial intelligence→人工智能//artificial light→人造光</t>
-  </si>
-  <si>
-    <t>雅思//GRE//商务</t>
-  </si>
-  <si>
-    <t>考研//雅思//托福</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>example</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>客观事实或某种规律</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去的某个时间点，发生的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将来的某个时间点，发生的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在过去的时间说，将来的某个时间点，发生的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在，已经完成的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在，正在发生的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去的某个时间点，正在发生的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>将来的某个时间点，正在发生的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在过去的时间说，将来的某个时间点，正在发生的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在，已经完成(一段时间)并且还在持续进行的动作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般过去时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般现在时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般将来时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去将来时</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -138,6 +829,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -154,7 +851,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -162,9 +859,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -177,6 +876,504 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>402772</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>933815</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1" descr="图片">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD2AD74F-18AF-69BE-512E-7E6976E7A481}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1807029" y="3265715"/>
+          <a:ext cx="7051586" cy="11274334"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB426F10-AE24-5B52-C9FB-943D73B09434}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9144000" cy="12077700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0DA7E88-0726-5282-97B0-FD7203CFA88B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9144000" y="0"/>
+          <a:ext cx="9144000" cy="11910060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14D5CFA2-D171-5555-41F2-3CDA51DCB356}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="18288000" y="0"/>
+          <a:ext cx="9144000" cy="11910060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>60</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B853C5C-5BC7-AFC0-379D-2853D84C561A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="27432000" y="0"/>
+          <a:ext cx="9144000" cy="11963400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>60</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52AAAC17-95BD-376C-3F98-CC8116C6B01A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="36576000" y="0"/>
+          <a:ext cx="9144000" cy="12039600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>90</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59C45707-4477-B761-B251-7671DC56CF4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="45720000" y="0"/>
+          <a:ext cx="9144000" cy="11910060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>90</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>105</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF76B74E-D5B5-A0FD-4A9E-8B6797C165FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="54864000" y="0"/>
+          <a:ext cx="9144000" cy="11910060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -442,17 +1639,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="1" customWidth="1"/>
-    <col min="4" max="5" width="9.140625" style="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="32.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="31.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="9.109375" style="1"/>
+    <col min="6" max="6" width="13.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="31.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -469,78 +1669,834 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>22</v>
+      <c r="F6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{2114160C-8A15-4EA8-A16C-B04888845BCC}">
+      <formula1>class</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAEC8DAE-FDCE-4317-BC8D-AE9BC9EECB2F}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572071EC-330F-497E-886C-968D88F1295D}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21.21875" customWidth="1"/>
+    <col min="4" max="4" width="62.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="57.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>164</v>
+      </c>
+      <c r="E16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>166</v>
+      </c>
+      <c r="E17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4182AD1-FDD0-4AE5-805D-56D655041C90}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/public/docs/datas/words.xlsx
+++ b/public/docs/datas/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FC5ADD-5717-4EBB-B768-2807F9D5425C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CFA961-73A9-402E-9701-7B85889E63B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32820" yWindow="7455" windowWidth="28500" windowHeight="13005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31740" yWindow="6180" windowWidth="28500" windowHeight="13005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="words" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="1042">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="1067">
   <si>
     <t>word</t>
   </si>
@@ -4491,6 +4491,81 @@
   </si>
   <si>
     <t>doubt about→对…的疑虑//beyond doubt→毋庸置疑</t>
+  </si>
+  <si>
+    <t>pace</t>
+  </si>
+  <si>
+    <t>pace-'[步伐，速度]'</t>
+  </si>
+  <si>
+    <t>He walked at a slow pace.→他走得很慢。</t>
+  </si>
+  <si>
+    <t>keep pace with→跟上…的步伐//set the pace→定下节奏</t>
+  </si>
+  <si>
+    <t>pace/paces/paced/pacing</t>
+  </si>
+  <si>
+    <t>步伐</t>
+  </si>
+  <si>
+    <t>踱步；调整步伐</t>
+  </si>
+  <si>
+    <t>He paced nervously around the room.→他在房间里紧张地踱来踱去。</t>
+  </si>
+  <si>
+    <t>especially</t>
+  </si>
+  <si>
+    <t>来自 old French 'especial' + -ly</t>
+  </si>
+  <si>
+    <t>esp/尤其/特别</t>
+  </si>
+  <si>
+    <t>特别；尤其</t>
+  </si>
+  <si>
+    <t>He is especially talented in mathematics.→他在数学方面特别有天赋。</t>
+  </si>
+  <si>
+    <t>climate</t>
+  </si>
+  <si>
+    <t>源自拉丁语 'clima'（气候、区域）</t>
+  </si>
+  <si>
+    <t>weather//atmosphere</t>
+  </si>
+  <si>
+    <t>气候；环境</t>
+  </si>
+  <si>
+    <t>The climate in this region is very humid.→该地区的气候非常潮湿。</t>
+  </si>
+  <si>
+    <t>climate change→气候变化//climate zone→气候带</t>
+  </si>
+  <si>
+    <t>scientific</t>
+  </si>
+  <si>
+    <t>源自拉丁语 'scientia'（知识、学问）</t>
+  </si>
+  <si>
+    <t>knowledge//study</t>
+  </si>
+  <si>
+    <t>科学的；系统的</t>
+  </si>
+  <si>
+    <t>Scientific research requires rigorous methodology.→科学研究需要严格的方法论。</t>
+  </si>
+  <si>
+    <t>scientific method→科学方法//scientific study→科学研究</t>
   </si>
 </sst>
 </file>
@@ -4566,7 +4641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4587,6 +4662,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5369,7 +5447,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:J147"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" style="1" customWidth="1"/>
@@ -9320,7 +9398,7 @@
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="6"/>
-      <c r="E146" s="6" t="s">
+      <c r="E146" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F146" s="6" t="s">
@@ -9361,6 +9439,124 @@
       </c>
       <c r="I147" s="6" t="s">
         <v>787</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" s="9" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="30">
+      <c r="A149" s="9" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="30">
+      <c r="A150" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="30">
+      <c r="A152" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>1066</v>
       </c>
     </row>
   </sheetData>
@@ -9371,7 +9567,7 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E11 E145 F146 E147:E1048576" xr:uid="{2114160C-8A15-4EA8-A16C-B04888845BCC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E11 F146 E145:E1048576" xr:uid="{2114160C-8A15-4EA8-A16C-B04888845BCC}">
       <formula1>class</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/docs/datas/words.xlsx
+++ b/public/docs/datas/words.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CFA961-73A9-402E-9701-7B85889E63B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51B5FCE-54DF-4F58-8E19-BC944342CCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31740" yWindow="6180" windowWidth="28500" windowHeight="13005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30945" yWindow="5445" windowWidth="16890" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="words" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="1328">
   <si>
     <t>word</t>
   </si>
@@ -2771,21 +2771,6 @@
     <t>set</t>
   </si>
   <si>
-    <t>set–set–set</t>
-  </si>
-  <si>
-    <t>setting</t>
-  </si>
-  <si>
-    <t>设置，放置</t>
-  </si>
-  <si>
-    <t>She set the table.→她摆好了餐具。</t>
-  </si>
-  <si>
-    <t>set up→建立//set off→出发</t>
-  </si>
-  <si>
     <t>show</t>
   </si>
   <si>
@@ -4566,6 +4551,804 @@
   </si>
   <si>
     <t>scientific method→科学方法//scientific study→科学研究</t>
+  </si>
+  <si>
+    <t>mingle</t>
+  </si>
+  <si>
+    <t>literature</t>
+  </si>
+  <si>
+    <t>stimulate</t>
+  </si>
+  <si>
+    <t>可能源自中古英语 'myngen'（混合）</t>
+  </si>
+  <si>
+    <t>mingle//mingles//mingled//mingling</t>
+  </si>
+  <si>
+    <t>blend//mix</t>
+  </si>
+  <si>
+    <t>使混合；使联结</t>
+  </si>
+  <si>
+    <t>六级//雅思</t>
+  </si>
+  <si>
+    <t>She mingled the ingredients to make a new flavor.→她把这些原料混合在一起创造了新口味。</t>
+  </si>
+  <si>
+    <t>mingle with→与...交往//mingle together→混合在一起</t>
+  </si>
+  <si>
+    <t>古英语 'settan'（放置）</t>
+  </si>
+  <si>
+    <t>set//sets//setting//set</t>
+  </si>
+  <si>
+    <t>place//fix</t>
+  </si>
+  <si>
+    <t>高中//雅思//GRE</t>
+  </si>
+  <si>
+    <t>一套；集合</t>
+  </si>
+  <si>
+    <t>高中//四级</t>
+  </si>
+  <si>
+    <t>A set of tools is required for the job.→这项工作需要一套工具。</t>
+  </si>
+  <si>
+    <t>TV set→电视机//a set of rules→一套规则</t>
+  </si>
+  <si>
+    <t>拉丁语 'litera'（文字）</t>
+  </si>
+  <si>
+    <t>文学；文献</t>
+  </si>
+  <si>
+    <t>四级//雅思</t>
+  </si>
+  <si>
+    <t>English literature is taught worldwide.→英语文学在全世界都被教授。</t>
+  </si>
+  <si>
+    <t>world literature→世界文学//classical literature→古典文学</t>
+  </si>
+  <si>
+    <t>hypothesis</t>
+  </si>
+  <si>
+    <t>希腊语 'hypo'（在下）+'thesis'（放置）</t>
+  </si>
+  <si>
+    <t>假设；前提</t>
+  </si>
+  <si>
+    <t>六级//GRE</t>
+  </si>
+  <si>
+    <t>The experiment confirmed the scientist’s hypothesis.→实验验证了科学家的假设。</t>
+  </si>
+  <si>
+    <t>test a hypothesis→验证假设//null hypothesis→零假设</t>
+  </si>
+  <si>
+    <t>suggest</t>
+  </si>
+  <si>
+    <t>拉丁语 'suggerere'（提出）</t>
+  </si>
+  <si>
+    <t>suggest//suggests//suggested//suggesting</t>
+  </si>
+  <si>
+    <t>recommend//propose</t>
+  </si>
+  <si>
+    <t>建议；暗示</t>
+  </si>
+  <si>
+    <t>四级//雅思//GRE</t>
+  </si>
+  <si>
+    <t>He suggested going for a walk.→他建议去散步。</t>
+  </si>
+  <si>
+    <t>suggest that→建议...//suggest itself→自然而然地出现</t>
+  </si>
+  <si>
+    <t>拉丁语 'stimulare'（刺激）</t>
+  </si>
+  <si>
+    <t>stimulate//stimulates//stimulated//stimulating</t>
+  </si>
+  <si>
+    <t>encourage//motivate</t>
+  </si>
+  <si>
+    <t>刺激；促进</t>
+  </si>
+  <si>
+    <t>The teacher's words stimulated her interest in science.→老师的话激发了她对科学的兴趣。</t>
+  </si>
+  <si>
+    <t>stimulate growth→促进增长//stimulate interest→激发兴趣</t>
+  </si>
+  <si>
+    <t>interdisciplinary</t>
+  </si>
+  <si>
+    <t>inter-(相互)+discipline(学科)+-ary(形容)</t>
+  </si>
+  <si>
+    <t>跨学科的</t>
+  </si>
+  <si>
+    <t>The project takes an interdisciplinary approach.→该项目采用了跨学科的方法。</t>
+  </si>
+  <si>
+    <t>interdisciplinary research→跨学科研究</t>
+  </si>
+  <si>
+    <t>foster</t>
+  </si>
+  <si>
+    <t>古英语 'fostrian'（养育）</t>
+  </si>
+  <si>
+    <t>foster//fosters//fostered//fostering</t>
+  </si>
+  <si>
+    <t>encourage//cultivate</t>
+  </si>
+  <si>
+    <t>促进；培养</t>
+  </si>
+  <si>
+    <t>The school aims to foster creativity.→学校旨在培养创造力。</t>
+  </si>
+  <si>
+    <t>foster talent→培养人才//foster cooperation→促进合作</t>
+  </si>
+  <si>
+    <t>boundary</t>
+  </si>
+  <si>
+    <t>古英语 'bound'（边界）+'ary'</t>
+  </si>
+  <si>
+    <t>边界；界限</t>
+  </si>
+  <si>
+    <t>The river forms the boundary between two countries.→这条河构成了两国的边界。</t>
+  </si>
+  <si>
+    <t>national boundary→国界//boundary line→边界线</t>
+  </si>
+  <si>
+    <t>field</t>
+  </si>
+  <si>
+    <t>古英语 'feld'（空旷的土地）</t>
+  </si>
+  <si>
+    <t>领域；田地</t>
+  </si>
+  <si>
+    <t>He is a well-known expert in the field of physics.→他是物理学领域的知名专家。</t>
+  </si>
+  <si>
+    <t>field research→实地调查//magnetic field→磁场</t>
+  </si>
+  <si>
+    <t>设置，放置；设定</t>
+  </si>
+  <si>
+    <t>She set the table.→她摆好了餐具。//He set the keys on the table.→他把钥匙放在桌上。</t>
+  </si>
+  <si>
+    <t>set up→建立//set out→出发//set aside→留出//set off→出发；触发；扣除；抵消；装饰</t>
+  </si>
+  <si>
+    <t>blind</t>
+  </si>
+  <si>
+    <t>blind//blinds//blinded//blinding</t>
+  </si>
+  <si>
+    <t>visionless</t>
+  </si>
+  <si>
+    <t>瞎的；盲目的</t>
+  </si>
+  <si>
+    <t>He is blind in one eye.→他一只眼睛失明。</t>
+  </si>
+  <si>
+    <t>blind spot→盲点//go blind→失明</t>
+  </si>
+  <si>
+    <t>使失明；蒙蔽</t>
+  </si>
+  <si>
+    <t>四级//六级</t>
+  </si>
+  <si>
+    <t>The strong light blinded him for a moment.→强光让他一时看不见东西。</t>
+  </si>
+  <si>
+    <t>blind with anger→被愤怒蒙蔽</t>
+  </si>
+  <si>
+    <t>spot</t>
+  </si>
+  <si>
+    <t>spot//spots//spotted//spotting</t>
+  </si>
+  <si>
+    <t>dot//mark</t>
+  </si>
+  <si>
+    <t>斑点；地点</t>
+  </si>
+  <si>
+    <t>There is a red spot on the shirt.→衬衫上有一个红点。</t>
+  </si>
+  <si>
+    <t>parking spot→停车位//tourist spot→旅游景点</t>
+  </si>
+  <si>
+    <t>发现；认出</t>
+  </si>
+  <si>
+    <t>She spotted her friend in the crowd.→她在人群中认出了朋友。</t>
+  </si>
+  <si>
+    <t>spot a mistake→发现错误</t>
+  </si>
+  <si>
+    <t>biology</t>
+  </si>
+  <si>
+    <t>生物学</t>
+  </si>
+  <si>
+    <t>Biology is her favorite subject.→生物学是她最喜欢的学科。</t>
+  </si>
+  <si>
+    <t>attached</t>
+  </si>
+  <si>
+    <t>attach//attaches//attached//attaching</t>
+  </si>
+  <si>
+    <t>connect</t>
+  </si>
+  <si>
+    <t>附上；依恋</t>
+  </si>
+  <si>
+    <t>Please find the file attached.→请查收附件。</t>
+  </si>
+  <si>
+    <t>attached to→依恋于</t>
+  </si>
+  <si>
+    <t>replicate</t>
+  </si>
+  <si>
+    <t>replicate//replicates//replicated//replicating</t>
+  </si>
+  <si>
+    <t>copy</t>
+  </si>
+  <si>
+    <t>复制；重复实验</t>
+  </si>
+  <si>
+    <t>They tried to replicate the experiment.→他们尝试重复实验。</t>
+  </si>
+  <si>
+    <t>replicate results→重复结果</t>
+  </si>
+  <si>
+    <t>scale//scales//scaled//scaling</t>
+  </si>
+  <si>
+    <t>measure</t>
+  </si>
+  <si>
+    <t>规模；比例；刻度</t>
+  </si>
+  <si>
+    <t>The company is growing on a large scale.→公司正在大规模发展。</t>
+  </si>
+  <si>
+    <t>on a global scale→在全球范围内//scale of measurement→测量刻度</t>
+  </si>
+  <si>
+    <t>攀登；缩放</t>
+  </si>
+  <si>
+    <t>They scaled the mountain quickly.→他们迅速攀登上山。</t>
+  </si>
+  <si>
+    <t>scale up→扩大//scale down→缩小</t>
+  </si>
+  <si>
+    <t>avenue</t>
+  </si>
+  <si>
+    <t>大道；途径</t>
+  </si>
+  <si>
+    <t>We walked along the tree-lined avenue.→我们走在林荫大道上。</t>
+  </si>
+  <si>
+    <t>avenue of approach→途径//Fifth Avenue→第五大道</t>
+  </si>
+  <si>
+    <t>feasible</t>
+  </si>
+  <si>
+    <t>可行的；可能的</t>
+  </si>
+  <si>
+    <t>The plan is economically feasible.→这个计划在经济上是可行的。</t>
+  </si>
+  <si>
+    <t>feasible solution→可行的解决方案</t>
+  </si>
+  <si>
+    <t>sociological</t>
+  </si>
+  <si>
+    <t>社会学的</t>
+  </si>
+  <si>
+    <t>She wrote a sociological analysis of urban life.→她写了一篇关于城市生活的社会学分析。</t>
+  </si>
+  <si>
+    <t>sociological study→社会学研究</t>
+  </si>
+  <si>
+    <t>embrace</t>
+  </si>
+  <si>
+    <t>embrace//embraces//embraced//embracing</t>
+  </si>
+  <si>
+    <t>accept//hug</t>
+  </si>
+  <si>
+    <t>拥抱；接受</t>
+  </si>
+  <si>
+    <t>They embraced each other warmly.→他们热情地拥抱在一起。</t>
+  </si>
+  <si>
+    <t>embrace change→接受改变</t>
+  </si>
+  <si>
+    <t>拥抱</t>
+  </si>
+  <si>
+    <t>She gave him a warm embrace.→她给了他一个热烈的拥抱。</t>
+  </si>
+  <si>
+    <t>in the embrace of→在...怀抱中</t>
+  </si>
+  <si>
+    <t>cell biology→细胞生物学//marine biology→海洋生物学//systems biology→系统生物学</t>
+  </si>
+  <si>
+    <t>body</t>
+  </si>
+  <si>
+    <t>古英语 bodig（身体）</t>
+  </si>
+  <si>
+    <t>身体；主体；团体</t>
+  </si>
+  <si>
+    <t>通用</t>
+  </si>
+  <si>
+    <t>He has a strong body.→他有一个强壮的身体。</t>
+  </si>
+  <si>
+    <t>governing body→管理机构//student body→学生群体//a body of evidence→一堆证据</t>
+  </si>
+  <si>
+    <t>press</t>
+  </si>
+  <si>
+    <t>拉丁 premere（压）</t>
+  </si>
+  <si>
+    <t>past: pressed; p.p.: pressed</t>
+  </si>
+  <si>
+    <t>pressure//pressing</t>
+  </si>
+  <si>
+    <t>新闻界；出版社</t>
+  </si>
+  <si>
+    <t>The story was widely reported in the press.→这则新闻在媒体广泛报道。</t>
+  </si>
+  <si>
+    <t>the press conference→新闻发布会</t>
+  </si>
+  <si>
+    <t>按；压；敦促</t>
+  </si>
+  <si>
+    <t>He pressed the button to start the machine.→他按下按钮启动了机器。</t>
+  </si>
+  <si>
+    <t>integration</t>
+  </si>
+  <si>
+    <t>拉丁 integer（完整的）</t>
+  </si>
+  <si>
+    <t>整合；融合</t>
+  </si>
+  <si>
+    <t>学术//社会</t>
+  </si>
+  <si>
+    <t>The integration of new technologies is essential.→新技术的融合是必要的。</t>
+  </si>
+  <si>
+    <t>economic integration→经济一体化//social integration→社会融合</t>
+  </si>
+  <si>
+    <t>smarts</t>
+  </si>
+  <si>
+    <t>古英语 smeortan（刺痛，引申为聪明）</t>
+  </si>
+  <si>
+    <t>智慧；才智</t>
+  </si>
+  <si>
+    <t>非正式//口语</t>
+  </si>
+  <si>
+    <t>He’s got the smarts to solve it.→他有解决问题的聪明才智。</t>
+  </si>
+  <si>
+    <t>book smarts→书本智慧//street smarts→社会智慧</t>
+  </si>
+  <si>
+    <t>robotics</t>
+  </si>
+  <si>
+    <t>robot（机器人）+'ics'(学科)</t>
+  </si>
+  <si>
+    <t>机器人学</t>
+  </si>
+  <si>
+    <t>科技//学术</t>
+  </si>
+  <si>
+    <t>Robotics is advancing rapidly.→机器人学正在快速发展。</t>
+  </si>
+  <si>
+    <t>industrial robotics→工业机器人学//medical robotics→医疗机器人学</t>
+  </si>
+  <si>
+    <t>chip</t>
+  </si>
+  <si>
+    <t>中古英语 chip（木屑，引申为小片）</t>
+  </si>
+  <si>
+    <t>past: chipped; p.p.: chipped</t>
+  </si>
+  <si>
+    <t>microchip//chipset</t>
+  </si>
+  <si>
+    <t>芯片；碎片</t>
+  </si>
+  <si>
+    <t>科技//通用</t>
+  </si>
+  <si>
+    <t>The phone uses the latest chip.→这款手机使用了最新的芯片。</t>
+  </si>
+  <si>
+    <t>potato chip→薯片//credit card chip→信用卡芯片</t>
+  </si>
+  <si>
+    <t>削；凿；崩缺</t>
+  </si>
+  <si>
+    <t>The cup was chipped at the rim.→杯口缺了一角。</t>
+  </si>
+  <si>
+    <t>chip away at→逐渐削弱//chip in→凑钱；插话</t>
+  </si>
+  <si>
+    <t>polymath</t>
+  </si>
+  <si>
+    <t>希腊 poly-（多）+ math（学习）</t>
+  </si>
+  <si>
+    <t>博学者；通才</t>
+  </si>
+  <si>
+    <t>学术//文学</t>
+  </si>
+  <si>
+    <t>Leonardo da Vinci was a true polymath.→达·芬奇是真正的博学者。</t>
+  </si>
+  <si>
+    <t>Renaissance polymath→文艺复兴时期的通才</t>
+  </si>
+  <si>
+    <t>advent</t>
+  </si>
+  <si>
+    <t>拉丁 ad-（到来）+ venire（来）</t>
+  </si>
+  <si>
+    <t>到来；出现</t>
+  </si>
+  <si>
+    <t>学术//通用</t>
+  </si>
+  <si>
+    <t>The advent of the Internet changed everything.→互联网的到来改变了一切。</t>
+  </si>
+  <si>
+    <t>the advent of technology→技术的出现</t>
+  </si>
+  <si>
+    <t>organ</t>
+  </si>
+  <si>
+    <t>希腊 organon（工具，器官）</t>
+  </si>
+  <si>
+    <t>器官；机构</t>
+  </si>
+  <si>
+    <t>医学//音乐</t>
+  </si>
+  <si>
+    <t>The heart is a vital organ.→心脏是重要的器官。</t>
+  </si>
+  <si>
+    <t>organ transplant→器官移植//government organ→政府机构</t>
+  </si>
+  <si>
+    <t>inaccessible</t>
+  </si>
+  <si>
+    <t>in-（否定）+ access（进入）+'-ible'（形容词后缀）</t>
+  </si>
+  <si>
+    <t>难以接近的；不可理解的</t>
+  </si>
+  <si>
+    <t>The mountain peak is inaccessible in winter.→这座山峰冬天无法到达。</t>
+  </si>
+  <si>
+    <t>inaccessible terrain→难以进入的地形//inaccessible information→难以理解的信息</t>
+  </si>
+  <si>
+    <t>press for sth.→迫切要求，催促//press ahead→加紧进行</t>
+  </si>
+  <si>
+    <t>toolkit</t>
+  </si>
+  <si>
+    <t>realm</t>
+  </si>
+  <si>
+    <t>拉丁 regalis（王权）</t>
+  </si>
+  <si>
+    <t>领域；王国</t>
+  </si>
+  <si>
+    <t>The realm of science is vast.→科学领域广阔。</t>
+  </si>
+  <si>
+    <t>political realm→政治领域//realm of possibility→可能性范围</t>
+  </si>
+  <si>
+    <t>prodigious</t>
+  </si>
+  <si>
+    <t>拉丁 prodigium（预兆）</t>
+  </si>
+  <si>
+    <t>巨大的；惊人的</t>
+  </si>
+  <si>
+    <t>She has a prodigious talent for music.→她有惊人的音乐天赋。</t>
+  </si>
+  <si>
+    <t>prodigious amount→大量//prodigious feat→惊人壮举</t>
+  </si>
+  <si>
+    <t>successor</t>
+  </si>
+  <si>
+    <t>拉丁 succedere（接替）</t>
+  </si>
+  <si>
+    <t>继任者；后继者</t>
+  </si>
+  <si>
+    <t>He is the successor to the CEO position.→他是 CEO 的继任者。</t>
+  </si>
+  <si>
+    <t>heir and successor→继承人//successor company→继承公司</t>
+  </si>
+  <si>
+    <t>tool（工具）+'kit'(套件)</t>
+  </si>
+  <si>
+    <t>工具包；技能集</t>
+  </si>
+  <si>
+    <t>The new software comes with a powerful toolkit.→新软件附带强大的工具包。</t>
+  </si>
+  <si>
+    <t>software toolkit→软件工具包//developer toolkit→开发者工具包</t>
+  </si>
+  <si>
+    <t>poise</t>
+  </si>
+  <si>
+    <t>古法语 pois（重量，引申为沉着）</t>
+  </si>
+  <si>
+    <t>past: poised; p.p.: poised</t>
+  </si>
+  <si>
+    <t>沉着；稳重</t>
+  </si>
+  <si>
+    <t>She maintained her poise during the interview.→她在面试中保持沉着。</t>
+  </si>
+  <si>
+    <t>poise under pressure→压力下的沉着//poise oneself→调整姿态</t>
+  </si>
+  <si>
+    <t>mechanism</t>
+  </si>
+  <si>
+    <t>希腊 mechanē（装置，机制）</t>
+  </si>
+  <si>
+    <t>机制；原理；机械装置</t>
+  </si>
+  <si>
+    <t>The mechanism of the machine is quite complex.→这台机器的机械结构相当复杂。</t>
+  </si>
+  <si>
+    <t>defense mechanism→防御机制//mechanism of action→作用机制</t>
+  </si>
+  <si>
+    <t>indeed</t>
+  </si>
+  <si>
+    <t>确实；真的；甚至</t>
+  </si>
+  <si>
+    <t>It is indeed a remarkable achievement.→这确实是一项了不起的成就。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>favour</t>
+  </si>
+  <si>
+    <t>来自拉丁语 "favorem"，意为“支持、好意”</t>
+  </si>
+  <si>
+    <t>favours//favoured//favouring</t>
+  </si>
+  <si>
+    <t>favor</t>
+  </si>
+  <si>
+    <t>支持；偏爱；有利于</t>
+  </si>
+  <si>
+    <t>She favours classical music over pop.→她偏爱古典音乐而非流行音乐。</t>
+  </si>
+  <si>
+    <t>favour someone→偏爱某人//do someone a favour→帮某人一个忙</t>
+  </si>
+  <si>
+    <t>observation</t>
+  </si>
+  <si>
+    <t>observes//observed//observing</t>
+  </si>
+  <si>
+    <t>observe</t>
+  </si>
+  <si>
+    <t>观察；注意；观测</t>
+  </si>
+  <si>
+    <t>Her careful observation revealed the mistake.→她仔细的观察发现了错误。</t>
+  </si>
+  <si>
+    <t>make an observation→作出观察//keen observation→敏锐的观察</t>
+  </si>
+  <si>
+    <t>journal</t>
+  </si>
+  <si>
+    <t>journals//journaled//journaling</t>
+  </si>
+  <si>
+    <t>journaling</t>
+  </si>
+  <si>
+    <t>日记；期刊；记录</t>
+  </si>
+  <si>
+    <t>She kept a daily journal during her travels.→她在旅行期间每天写日记。</t>
+  </si>
+  <si>
+    <t>keep a journal→写日记//scientific journal→科学期刊</t>
+  </si>
+  <si>
+    <t>rapid</t>
+  </si>
+  <si>
+    <t>rapids//rapided//rapiding</t>
+  </si>
+  <si>
+    <t>quick/fast</t>
+  </si>
+  <si>
+    <t>快速的；急促的</t>
+  </si>
+  <si>
+    <t>The river's rapid current made boating dangerous.→河流湍急，使划船很危险。</t>
+  </si>
+  <si>
+    <t>rapid growth→快速增长//rapid response→迅速反应</t>
+  </si>
+  <si>
+    <t>particular</t>
+  </si>
+  <si>
+    <t>particulars//particulared//particularing</t>
+  </si>
+  <si>
+    <t>specific/special</t>
+  </si>
+  <si>
+    <t>特定的；特别的；讲究的</t>
+  </si>
+  <si>
+    <t>She was very particular about her clothes.→她对自己的衣服非常讲究。</t>
+  </si>
+  <si>
+    <t>particular attention→特别注意//in particular→尤其</t>
   </si>
 </sst>
 </file>
@@ -4603,7 +5386,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4628,6 +5411,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4641,7 +5430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4664,6 +5453,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5447,7 +6239,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" style="1" customWidth="1"/>
@@ -5524,56 +6316,56 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="6" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30">
       <c r="A4" s="6" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30">
@@ -5605,64 +6397,64 @@
     </row>
     <row r="6" spans="1:10" ht="30">
       <c r="A6" s="6" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30">
       <c r="A7" s="6" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30">
       <c r="A8" s="6" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -5670,16 +6462,16 @@
         <v>13</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30">
@@ -5760,10 +6552,10 @@
     </row>
     <row r="12" spans="1:10" ht="30">
       <c r="A12" s="6" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -5771,16 +6563,16 @@
         <v>13</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30">
@@ -5920,3654 +6712,4799 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="30">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="30">
+      <c r="A19" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B19" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C19" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D19" s="6" t="s">
         <v>460</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="45">
-      <c r="A19" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>423</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>425</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>426</v>
+        <v>461</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="45">
       <c r="A20" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="B20" s="7"/>
+        <v>422</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>423</v>
+      </c>
       <c r="C20" s="6" t="s">
-        <v>465</v>
+        <v>424</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F20" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G21" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>470</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="30">
-      <c r="A21" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>894</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6" t="s">
-        <v>895</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>896</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>897</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="30">
       <c r="A22" s="6" t="s">
-        <v>788</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>790</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="C22" s="6"/>
       <c r="D22" s="6" t="s">
-        <v>791</v>
+        <v>890</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>792</v>
+        <v>891</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>793</v>
+        <v>844</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>794</v>
+        <v>892</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="30">
       <c r="A23" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="B23" s="7"/>
+        <v>783</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>784</v>
+      </c>
       <c r="C23" s="6" t="s">
-        <v>472</v>
+        <v>785</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>473</v>
+        <v>786</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F23" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G24" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="30">
-      <c r="A24" s="6" t="s">
+    <row r="25" spans="1:9" ht="30">
+      <c r="A25" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6" t="s">
+        <v>938</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>941</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>942</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6" t="s">
-        <v>943</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>944</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>945</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="6" t="s">
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B26" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C26" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E26" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F26" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I26" s="6" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="45">
-      <c r="A26" s="1" t="s">
+    <row r="27" spans="1:9" ht="45">
+      <c r="A27" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>1029</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>1034</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="6" t="s">
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B28" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C28" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D28" s="6" t="s">
         <v>487</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="30">
-      <c r="A28" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>310</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>311</v>
+        <v>488</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>236</v>
+        <v>446</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>312</v>
+        <v>489</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>313</v>
+        <v>490</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="30">
       <c r="A29" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
+      <c r="B29" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>310</v>
+      </c>
       <c r="E29" s="6" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>236</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30">
-      <c r="A30" s="6" t="s">
-        <v>977</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>978</v>
-      </c>
+      <c r="A30" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B30" s="6"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="6" t="s">
-        <v>979</v>
-      </c>
+      <c r="D30" s="6"/>
       <c r="E30" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>980</v>
+        <v>314</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>849</v>
+        <v>236</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>981</v>
+        <v>315</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="30">
+      <c r="A31" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="30">
+      <c r="A32" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6" t="s">
+        <v>974</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>975</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>976</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B33" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C33" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D33" s="6" t="s">
         <v>494</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>501</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="45">
-      <c r="A33" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>347</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>348</v>
+        <v>495</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>236</v>
+        <v>468</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>349</v>
+        <v>496</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>350</v>
+        <v>497</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="6" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F34" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="45">
+      <c r="A35" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G36" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I36" s="6" t="s">
         <v>510</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="30">
-      <c r="A35" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="45">
-      <c r="A36" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="30">
       <c r="A37" s="6" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F37" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="45">
+      <c r="A38" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="30">
+      <c r="A39" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="G39" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="H37" s="6" t="s">
+      <c r="H39" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I39" s="6" t="s">
         <v>200</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="30">
-      <c r="A39" s="1" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>1039</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>1040</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>518</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="B40" s="7"/>
       <c r="C40" s="6" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F40" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="30">
+      <c r="A41" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F42" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G42" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="H40" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I42" s="6" t="s">
         <v>523</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>525</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>528</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>529</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="30">
-      <c r="A42" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="6" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>536</v>
+        <v>446</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="30">
       <c r="A44" s="6" t="s">
-        <v>386</v>
+        <v>217</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>388</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C44" s="6"/>
       <c r="D44" s="6" t="s">
-        <v>389</v>
+        <v>234</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>184</v>
+        <v>8</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>390</v>
+        <v>235</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>236</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>391</v>
+        <v>237</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="30">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="6" t="s">
-        <v>865</v>
+        <v>531</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>866</v>
-      </c>
-      <c r="C45" s="6"/>
+        <v>532</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>533</v>
+      </c>
       <c r="D45" s="6" t="s">
-        <v>867</v>
+        <v>534</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>868</v>
+        <v>535</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>849</v>
+        <v>536</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>869</v>
+        <v>537</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>870</v>
+        <v>538</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="30">
       <c r="A46" s="6" t="s">
-        <v>337</v>
+        <v>386</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>338</v>
+        <v>387</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>339</v>
+        <v>388</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>340</v>
+        <v>389</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>341</v>
+        <v>390</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>236</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>343</v>
+        <v>392</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="30">
-      <c r="A47" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E47" s="6" t="s">
+      <c r="A47" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="30">
+      <c r="A48" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>540</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>541</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>542</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>184</v>
-      </c>
       <c r="F48" s="6" t="s">
-        <v>543</v>
+        <v>863</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>468</v>
+        <v>844</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>544</v>
+        <v>864</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="30">
       <c r="A49" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="B49" s="7"/>
+        <v>337</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>338</v>
+      </c>
       <c r="C49" s="6" t="s">
-        <v>547</v>
+        <v>339</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>548</v>
+        <v>340</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>549</v>
+        <v>341</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>446</v>
+        <v>236</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>550</v>
+        <v>342</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>551</v>
+        <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="30">
       <c r="A50" s="6" t="s">
-        <v>876</v>
+        <v>207</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>877</v>
+        <v>208</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>878</v>
+        <v>209</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>879</v>
+      <c r="F50" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>849</v>
+        <v>192</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>880</v>
+        <v>210</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>881</v>
+        <v>211</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="6" t="s">
-        <v>552</v>
-      </c>
-      <c r="B51" s="7"/>
+        <v>539</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>540</v>
+      </c>
       <c r="C51" s="6" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>468</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>559</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="B52" s="7"/>
       <c r="C52" s="6" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="30">
       <c r="A53" s="6" t="s">
-        <v>565</v>
+        <v>871</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>567</v>
-      </c>
+        <v>872</v>
+      </c>
+      <c r="C53" s="6"/>
       <c r="D53" s="6" t="s">
-        <v>568</v>
+        <v>873</v>
       </c>
       <c r="E53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>874</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="30">
+      <c r="A54" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="B55" s="7"/>
+      <c r="C55" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F53" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>570</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="30">
-      <c r="A54" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="F55" s="6" t="s">
-        <v>298</v>
+        <v>555</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>236</v>
+        <v>468</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="I55" s="6"/>
+        <v>556</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>557</v>
+      </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="6" t="s">
-        <v>994</v>
+        <v>558</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>995</v>
-      </c>
-      <c r="C56" s="6"/>
+        <v>559</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>560</v>
+      </c>
       <c r="D56" s="6" t="s">
-        <v>996</v>
+        <v>561</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>997</v>
+        <v>562</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>849</v>
+        <v>468</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>998</v>
+        <v>563</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>999</v>
+        <v>564</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="30">
       <c r="A57" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="B57" s="7"/>
+        <v>565</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>566</v>
+      </c>
       <c r="C57" s="6" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>446</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="30">
-      <c r="A58" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="B58" s="7"/>
-      <c r="C58" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E58" s="6" t="s">
+      <c r="A58" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>1017</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>1018</v>
+      <c r="F58" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>1116</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="30">
-      <c r="A59" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="B59" s="7"/>
+      <c r="A59" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>293</v>
+      </c>
       <c r="C59" s="6" t="s">
-        <v>581</v>
+        <v>294</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>582</v>
+        <v>295</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>583</v>
+        <v>296</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>536</v>
+        <v>236</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>584</v>
+        <v>297</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>585</v>
+        <v>300</v>
       </c>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="B60" s="7"/>
-      <c r="C60" s="6" t="s">
-        <v>587</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>588</v>
-      </c>
+      <c r="A60" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
       <c r="E60" s="6" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>589</v>
+        <v>298</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>468</v>
+        <v>236</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="30">
+        <v>299</v>
+      </c>
+      <c r="I60" s="6"/>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6" t="s">
-        <v>352</v>
-      </c>
+        <v>989</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>990</v>
+      </c>
+      <c r="C61" s="6"/>
       <c r="D61" s="6" t="s">
-        <v>353</v>
+        <v>991</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>354</v>
+        <v>992</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>236</v>
+        <v>844</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>355</v>
+        <v>993</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="30">
       <c r="A62" s="6" t="s">
-        <v>592</v>
+        <v>572</v>
       </c>
       <c r="B62" s="7"/>
       <c r="C62" s="6" t="s">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>594</v>
+        <v>574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>595</v>
+        <v>575</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>536</v>
+        <v>446</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="30">
       <c r="A63" s="6" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
       <c r="B63" s="7"/>
       <c r="C63" s="6" t="s">
-        <v>599</v>
+        <v>579</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>600</v>
+        <v>1011</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>468</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>602</v>
+        <v>1012</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>603</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="30">
-      <c r="A64" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>376</v>
-      </c>
+      <c r="A64" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B64" s="7"/>
       <c r="C64" s="6" t="s">
-        <v>377</v>
+        <v>581</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>378</v>
+        <v>582</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>414</v>
+        <v>583</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>236</v>
+        <v>536</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>415</v>
+        <v>584</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="30">
-      <c r="A65" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
+        <v>585</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="B65" s="7"/>
+      <c r="C65" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>588</v>
+      </c>
       <c r="E65" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>416</v>
+        <v>589</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>236</v>
+        <v>468</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="I65" s="6"/>
-    </row>
-    <row r="66" spans="1:9">
+        <v>590</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="30">
       <c r="A66" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="B66" s="7"/>
+        <v>351</v>
+      </c>
+      <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
-        <v>605</v>
+        <v>352</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>606</v>
+        <v>353</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>607</v>
+        <v>354</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>446</v>
+        <v>236</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>608</v>
+        <v>355</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="30">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="C67" s="6"/>
+        <v>592</v>
+      </c>
+      <c r="B67" s="7"/>
+      <c r="C67" s="6" t="s">
+        <v>593</v>
+      </c>
       <c r="D67" s="6" t="s">
-        <v>240</v>
+        <v>594</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>241</v>
+        <v>595</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>236</v>
+        <v>536</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>242</v>
+        <v>596</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="30">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" s="6" t="s">
-        <v>859</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>860</v>
-      </c>
-      <c r="C68" s="6"/>
+        <v>598</v>
+      </c>
+      <c r="B68" s="7"/>
+      <c r="C68" s="6" t="s">
+        <v>599</v>
+      </c>
       <c r="D68" s="6" t="s">
-        <v>861</v>
+        <v>600</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>8</v>
+        <v>184</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>862</v>
+        <v>601</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>849</v>
+        <v>468</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>863</v>
+        <v>602</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>864</v>
+        <v>603</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="30">
-      <c r="A69" s="6" t="s">
-        <v>12</v>
+      <c r="A69" s="8" t="s">
+        <v>375</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C69" s="6"/>
+        <v>376</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>377</v>
+      </c>
       <c r="D69" s="6" t="s">
-        <v>162</v>
+        <v>378</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>163</v>
+        <v>414</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>15</v>
+        <v>236</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>164</v>
+        <v>415</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>165</v>
+        <v>379</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="30">
-      <c r="A70" s="6" t="s">
-        <v>922</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>923</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>924</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>925</v>
-      </c>
+      <c r="A70" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
       <c r="E70" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>926</v>
+        <v>416</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>849</v>
+        <v>236</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>927</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>928</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="I70" s="6"/>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="6" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B71" s="7"/>
       <c r="C71" s="6" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="30">
       <c r="A72" s="6" t="s">
-        <v>616</v>
-      </c>
-      <c r="B72" s="7"/>
-      <c r="C72" s="6" t="s">
-        <v>617</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C72" s="6"/>
       <c r="D72" s="6" t="s">
-        <v>618</v>
+        <v>240</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>619</v>
+        <v>241</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>446</v>
+        <v>236</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>620</v>
+        <v>242</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>621</v>
+        <v>243</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="30">
-      <c r="A73" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="G73" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9">
+      <c r="A73" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="30">
       <c r="A74" s="6" t="s">
-        <v>622</v>
-      </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="6" t="s">
-        <v>623</v>
-      </c>
+        <v>854</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="C74" s="6"/>
       <c r="D74" s="6" t="s">
-        <v>624</v>
+        <v>856</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>184</v>
+        <v>8</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>625</v>
+        <v>857</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>468</v>
+        <v>844</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>626</v>
+        <v>858</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="30">
       <c r="A75" s="6" t="s">
-        <v>628</v>
-      </c>
-      <c r="B75" s="7"/>
-      <c r="C75" s="6" t="s">
-        <v>629</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C75" s="6"/>
       <c r="D75" s="6" t="s">
-        <v>630</v>
+        <v>162</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>631</v>
+        <v>163</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>446</v>
+        <v>15</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>632</v>
+        <v>164</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9">
-      <c r="A76" s="6" t="s">
-        <v>634</v>
-      </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="6" t="s">
-        <v>635</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>637</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="I76" s="6" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="30">
+      <c r="A76" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="30">
       <c r="A77" s="6" t="s">
-        <v>640</v>
-      </c>
-      <c r="B77" s="7"/>
+        <v>917</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>918</v>
+      </c>
       <c r="C77" s="6" t="s">
-        <v>641</v>
+        <v>919</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>642</v>
+        <v>920</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>643</v>
+        <v>921</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>468</v>
+        <v>844</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>644</v>
+        <v>922</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>645</v>
+        <v>923</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="6" t="s">
-        <v>646</v>
+        <v>610</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="6" t="s">
-        <v>647</v>
+        <v>611</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>648</v>
+        <v>612</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>649</v>
+        <v>613</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>468</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>650</v>
+        <v>614</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="45">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="C79" s="6"/>
+        <v>616</v>
+      </c>
+      <c r="B79" s="7"/>
+      <c r="C79" s="6" t="s">
+        <v>617</v>
+      </c>
       <c r="D79" s="6" t="s">
-        <v>245</v>
+        <v>618</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>279</v>
+        <v>619</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>236</v>
+        <v>446</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>246</v>
+        <v>620</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="30">
       <c r="A80" s="6" t="s">
-        <v>652</v>
-      </c>
-      <c r="B80" s="7"/>
+        <v>368</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>369</v>
+      </c>
       <c r="C80" s="6" t="s">
-        <v>653</v>
+        <v>370</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>654</v>
+        <v>371</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>655</v>
+        <v>372</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="B81" s="7"/>
+      <c r="C81" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="G81" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="H80" s="6" t="s">
-        <v>656</v>
-      </c>
-      <c r="I80" s="6" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="30">
-      <c r="A81" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>236</v>
-      </c>
       <c r="H81" s="6" t="s">
-        <v>288</v>
+        <v>626</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>289</v>
+        <v>627</v>
       </c>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
+      <c r="A82" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="B82" s="7"/>
+      <c r="C82" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>630</v>
+      </c>
       <c r="E82" s="6" t="s">
-        <v>8</v>
+        <v>184</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>290</v>
+        <v>631</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>236</v>
+        <v>446</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="I82" s="6"/>
-    </row>
-    <row r="83" spans="1:9" ht="30">
+        <v>632</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="C83" s="6"/>
+        <v>634</v>
+      </c>
+      <c r="B83" s="7"/>
+      <c r="C83" s="6" t="s">
+        <v>635</v>
+      </c>
       <c r="D83" s="6" t="s">
-        <v>249</v>
+        <v>636</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>250</v>
+        <v>637</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>236</v>
+        <v>468</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>251</v>
+        <v>638</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>252</v>
+        <v>639</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="6" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="B84" s="7"/>
       <c r="C84" s="6" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>660</v>
+        <v>642</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>468</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="30">
-      <c r="A85" s="6" t="s">
-        <v>807</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>808</v>
-      </c>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6" t="s">
+      <c r="A85" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="6" t="s">
-        <v>809</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>810</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="30">
+      <c r="F85" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
       <c r="A86" s="6" t="s">
-        <v>904</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>905</v>
-      </c>
-      <c r="C86" s="6"/>
+        <v>646</v>
+      </c>
+      <c r="B86" s="7"/>
+      <c r="C86" s="6" t="s">
+        <v>647</v>
+      </c>
       <c r="D86" s="6" t="s">
-        <v>906</v>
+        <v>648</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>907</v>
+        <v>649</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>849</v>
+        <v>468</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>908</v>
+        <v>650</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="30">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="45">
       <c r="A87" s="6" t="s">
-        <v>947</v>
+        <v>219</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>948</v>
+        <v>244</v>
       </c>
       <c r="C87" s="6"/>
       <c r="D87" s="6" t="s">
-        <v>949</v>
+        <v>245</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>950</v>
+        <v>279</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>849</v>
+        <v>236</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>951</v>
+        <v>246</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="30">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
       <c r="A88" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="C88" s="6"/>
+        <v>652</v>
+      </c>
+      <c r="B88" s="7"/>
+      <c r="C88" s="6" t="s">
+        <v>653</v>
+      </c>
       <c r="D88" s="6" t="s">
-        <v>395</v>
+        <v>654</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>396</v>
+        <v>655</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>236</v>
+        <v>468</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>397</v>
+        <v>656</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>398</v>
+        <v>657</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="30">
-      <c r="A89" s="6" t="s">
-        <v>221</v>
+      <c r="A89" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="C89" s="6"/>
       <c r="D89" s="6" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="G89" s="6" t="s">
         <v>236</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="30">
-      <c r="A90" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>358</v>
-      </c>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B90" s="6"/>
       <c r="C90" s="6"/>
-      <c r="D90" s="6" t="s">
-        <v>359</v>
-      </c>
+      <c r="D90" s="6"/>
       <c r="E90" s="6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="G90" s="6" t="s">
         <v>236</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>362</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="I90" s="6"/>
     </row>
     <row r="91" spans="1:9" ht="30">
       <c r="A91" s="6" t="s">
-        <v>971</v>
+        <v>220</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>972</v>
+        <v>248</v>
       </c>
       <c r="C91" s="6"/>
       <c r="D91" s="6" t="s">
-        <v>973</v>
+        <v>249</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>974</v>
+        <v>250</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>849</v>
+        <v>236</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>975</v>
+        <v>251</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>976</v>
+        <v>252</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="6" t="s">
-        <v>983</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>984</v>
-      </c>
-      <c r="C92" s="6"/>
+        <v>658</v>
+      </c>
+      <c r="B92" s="7"/>
+      <c r="C92" s="6" t="s">
+        <v>659</v>
+      </c>
       <c r="D92" s="6" t="s">
-        <v>985</v>
+        <v>660</v>
       </c>
       <c r="E92" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="30">
+      <c r="A93" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>803</v>
+      </c>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F92" s="6" t="s">
-        <v>986</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>987</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9">
-      <c r="A93" s="6" t="s">
-        <v>664</v>
-      </c>
-      <c r="B93" s="7"/>
-      <c r="C93" s="6" t="s">
-        <v>665</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>666</v>
-      </c>
-      <c r="E93" s="6" t="s">
+      <c r="F93" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="30">
+      <c r="A94" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F93" s="6" t="s">
-        <v>667</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>668</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9">
-      <c r="A94" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>840</v>
-      </c>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>841</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>842</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>843</v>
+      <c r="F94" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>1071</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="30">
       <c r="A95" s="6" t="s">
-        <v>882</v>
+        <v>899</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>883</v>
+        <v>900</v>
       </c>
       <c r="C95" s="6"/>
       <c r="D95" s="6" t="s">
-        <v>884</v>
+        <v>901</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>885</v>
+        <v>902</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>887</v>
+        <v>904</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="30">
-      <c r="A96" s="8" t="s">
-        <v>166</v>
+      <c r="A96" s="6" t="s">
+        <v>942</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>167</v>
+        <v>943</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="6" t="s">
-        <v>168</v>
+        <v>944</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>169</v>
+        <v>945</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>170</v>
+        <v>844</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>171</v>
+        <v>946</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="45">
-      <c r="A97" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B97" s="6"/>
+        <v>947</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="30">
+      <c r="A97" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>394</v>
+      </c>
       <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
+      <c r="D97" s="6" t="s">
+        <v>395</v>
+      </c>
       <c r="E97" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>212</v>
+        <v>396</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>213</v>
+        <v>397</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>214</v>
+        <v>398</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="30">
       <c r="A98" s="6" t="s">
-        <v>852</v>
+        <v>221</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>853</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>854</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="C98" s="6"/>
       <c r="D98" s="6" t="s">
-        <v>855</v>
+        <v>254</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>856</v>
+        <v>280</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>849</v>
+        <v>236</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>857</v>
+        <v>255</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="30">
-      <c r="A99" s="6" t="s">
-        <v>935</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>936</v>
-      </c>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6" t="s">
-        <v>937</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>938</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>939</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="45">
-      <c r="A100" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G99" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>1024</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>13</v>
+      <c r="H99" s="1" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="30">
+      <c r="A100" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>1025</v>
+        <v>1043</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="30">
       <c r="A101" s="6" t="s">
-        <v>953</v>
+        <v>357</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>954</v>
+        <v>358</v>
       </c>
       <c r="C101" s="6"/>
       <c r="D101" s="6" t="s">
-        <v>955</v>
+        <v>359</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>956</v>
+        <v>360</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>849</v>
+        <v>236</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>957</v>
+        <v>361</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>958</v>
+        <v>362</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="30">
       <c r="A102" s="6" t="s">
-        <v>989</v>
+        <v>966</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>990</v>
+        <v>967</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="6" t="s">
-        <v>991</v>
+        <v>968</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>992</v>
+        <v>969</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>993</v>
+        <v>970</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="30">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" s="6" t="s">
-        <v>827</v>
+        <v>978</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>829</v>
-      </c>
+        <v>979</v>
+      </c>
+      <c r="C103" s="6"/>
       <c r="D103" s="6" t="s">
-        <v>830</v>
+        <v>980</v>
       </c>
       <c r="E103" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>981</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="B104" s="7"/>
+      <c r="C104" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="E104" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F103" s="6" t="s">
-        <v>831</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>832</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="30">
-      <c r="A104" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="E104" s="6" t="s">
+      <c r="F104" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F104" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="30">
-      <c r="A105" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>259</v>
-      </c>
       <c r="F105" s="6" t="s">
-        <v>281</v>
+        <v>836</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>236</v>
+        <v>788</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>260</v>
+        <v>837</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>261</v>
+        <v>838</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="30">
       <c r="A106" s="6" t="s">
-        <v>670</v>
-      </c>
-      <c r="B106" s="7"/>
-      <c r="C106" s="6" t="s">
-        <v>671</v>
-      </c>
+        <v>877</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>878</v>
+      </c>
+      <c r="C106" s="6"/>
       <c r="D106" s="6" t="s">
-        <v>672</v>
+        <v>879</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>184</v>
+        <v>8</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>673</v>
+        <v>880</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>536</v>
+        <v>844</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>674</v>
+        <v>881</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>675</v>
+        <v>882</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="30">
-      <c r="A107" s="6" t="s">
-        <v>796</v>
+      <c r="A107" s="8" t="s">
+        <v>166</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>797</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>798</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C107" s="6"/>
       <c r="D107" s="6" t="s">
-        <v>799</v>
+        <v>168</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>184</v>
+        <v>8</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>800</v>
+        <v>169</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>793</v>
+        <v>170</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>801</v>
+        <v>171</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>802</v>
+        <v>172</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="45">
-      <c r="A108" s="6" t="s">
-        <v>844</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>845</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>846</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>847</v>
-      </c>
+      <c r="A108" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
       <c r="E108" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F108" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="I108" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="30">
+      <c r="A109" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="B109" s="6" t="s">
         <v>848</v>
       </c>
-      <c r="G108" s="6" t="s">
+      <c r="C109" s="6" t="s">
         <v>849</v>
       </c>
-      <c r="H108" s="6" t="s">
+      <c r="D109" s="6" t="s">
         <v>850</v>
       </c>
-      <c r="I108" s="6" t="s">
+      <c r="E109" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F109" s="6" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" ht="45">
-      <c r="A109" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>185</v>
-      </c>
       <c r="G109" s="6" t="s">
-        <v>15</v>
+        <v>844</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>186</v>
+        <v>852</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>187</v>
+        <v>853</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="30">
-      <c r="A110" s="8" t="s">
-        <v>327</v>
+      <c r="A110" s="6" t="s">
+        <v>930</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>329</v>
-      </c>
+        <v>931</v>
+      </c>
+      <c r="C110" s="6"/>
       <c r="D110" s="6" t="s">
-        <v>330</v>
+        <v>932</v>
       </c>
       <c r="E110" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="I110" s="6" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="45">
+      <c r="A111" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F110" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="G110" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="30">
-      <c r="A111" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="G111" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="I111" s="6" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9">
+      <c r="F111" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="30">
       <c r="A112" s="6" t="s">
-        <v>676</v>
-      </c>
-      <c r="B112" s="7"/>
-      <c r="C112" s="6" t="s">
-        <v>677</v>
-      </c>
+        <v>948</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="C112" s="6"/>
       <c r="D112" s="6" t="s">
-        <v>678</v>
+        <v>950</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>679</v>
+        <v>951</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>468</v>
+        <v>844</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>680</v>
+        <v>952</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="30">
       <c r="A113" s="6" t="s">
-        <v>682</v>
-      </c>
-      <c r="B113" s="7"/>
-      <c r="C113" s="6" t="s">
-        <v>683</v>
-      </c>
+        <v>984</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>985</v>
+      </c>
+      <c r="C113" s="6"/>
       <c r="D113" s="6" t="s">
-        <v>684</v>
+        <v>986</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>685</v>
+        <v>987</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>536</v>
+        <v>844</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>686</v>
+        <v>988</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>687</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="30">
       <c r="A114" s="6" t="s">
-        <v>871</v>
+        <v>822</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="C114" s="6"/>
+        <v>823</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>824</v>
+      </c>
       <c r="D114" s="6" t="s">
-        <v>873</v>
+        <v>825</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>874</v>
+        <v>826</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>849</v>
+        <v>788</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>875</v>
+        <v>827</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>1019</v>
+        <v>828</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="30">
       <c r="A115" s="6" t="s">
-        <v>301</v>
+        <v>380</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>302</v>
+        <v>381</v>
       </c>
       <c r="C115" s="6"/>
       <c r="D115" s="6" t="s">
-        <v>303</v>
+        <v>382</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>304</v>
+        <v>383</v>
       </c>
       <c r="G115" s="6" t="s">
         <v>236</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>305</v>
+        <v>384</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="30">
       <c r="A116" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="B116" s="7"/>
-      <c r="C116" s="6" t="s">
-        <v>688</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C116" s="6"/>
       <c r="D116" s="6" t="s">
-        <v>689</v>
+        <v>258</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>184</v>
+        <v>259</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>690</v>
+        <v>281</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>536</v>
+        <v>236</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>691</v>
+        <v>260</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="30">
       <c r="A117" s="6" t="s">
-        <v>693</v>
+        <v>670</v>
       </c>
       <c r="B117" s="7"/>
       <c r="C117" s="6" t="s">
-        <v>694</v>
+        <v>671</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>695</v>
+        <v>672</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>696</v>
+        <v>673</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>468</v>
+        <v>536</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>697</v>
+        <v>674</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="30">
       <c r="A118" s="6" t="s">
-        <v>699</v>
-      </c>
-      <c r="B118" s="7"/>
+        <v>791</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>792</v>
+      </c>
       <c r="C118" s="6" t="s">
-        <v>700</v>
+        <v>793</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>701</v>
+        <v>794</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>702</v>
+        <v>795</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>468</v>
+        <v>788</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>703</v>
+        <v>796</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="45">
       <c r="A119" s="6" t="s">
-        <v>705</v>
-      </c>
-      <c r="B119" s="7"/>
+        <v>839</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>840</v>
+      </c>
       <c r="C119" s="6" t="s">
-        <v>706</v>
+        <v>841</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>707</v>
+        <v>842</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>708</v>
+        <v>843</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>468</v>
+        <v>844</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>709</v>
+        <v>845</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="30">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="45">
       <c r="A120" s="6" t="s">
-        <v>711</v>
-      </c>
-      <c r="B120" s="7"/>
+        <v>180</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>181</v>
+      </c>
       <c r="C120" s="6" t="s">
-        <v>712</v>
+        <v>182</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>713</v>
+        <v>183</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>714</v>
+        <v>185</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>468</v>
+        <v>15</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>715</v>
+        <v>186</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9">
-      <c r="A121" s="6" t="s">
-        <v>964</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="30">
+      <c r="A121" s="8" t="s">
+        <v>327</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>965</v>
+        <v>328</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>966</v>
+        <v>329</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>967</v>
+        <v>330</v>
       </c>
       <c r="E121" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="I121" s="6" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="30">
+      <c r="A122" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="B122" s="6"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F121" s="6" t="s">
-        <v>968</v>
-      </c>
-      <c r="G121" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="H121" s="6" t="s">
-        <v>969</v>
-      </c>
-      <c r="I121" s="6" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="30">
-      <c r="A122" s="6" t="s">
-        <v>898</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>899</v>
-      </c>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6" t="s">
-        <v>900</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="F122" s="6" t="s">
-        <v>901</v>
+        <v>334</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>849</v>
+        <v>236</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>902</v>
+        <v>335</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>903</v>
+        <v>336</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="6" t="s">
-        <v>717</v>
+        <v>676</v>
       </c>
       <c r="B123" s="7"/>
       <c r="C123" s="6" t="s">
-        <v>718</v>
+        <v>677</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>719</v>
+        <v>678</v>
       </c>
       <c r="E123" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>720</v>
+        <v>679</v>
       </c>
       <c r="G123" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="I123" s="6" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="B124" s="7"/>
+      <c r="C124" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="G124" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="H123" s="6" t="s">
-        <v>721</v>
-      </c>
-      <c r="I123" s="6" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="30">
-      <c r="A124" s="6" t="s">
-        <v>959</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>960</v>
-      </c>
-      <c r="C124" s="6"/>
-      <c r="D124" s="6" t="s">
-        <v>961</v>
-      </c>
-      <c r="E124" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>962</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>849</v>
-      </c>
       <c r="H124" s="6" t="s">
-        <v>963</v>
+        <v>686</v>
       </c>
       <c r="I124" s="6" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="30">
+      <c r="A125" s="6" t="s">
+        <v>866</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="C125" s="6"/>
+      <c r="D125" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="I125" s="6" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
-      <c r="A125" s="6" t="s">
-        <v>723</v>
-      </c>
-      <c r="B125" s="7"/>
-      <c r="C125" s="6" t="s">
-        <v>724</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>725</v>
-      </c>
-      <c r="E125" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>726</v>
-      </c>
-      <c r="G125" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="H125" s="6" t="s">
-        <v>727</v>
-      </c>
-      <c r="I125" s="6" t="s">
-        <v>728</v>
-      </c>
-    </row>
     <row r="126" spans="1:9" ht="30">
-      <c r="A126" s="8" t="s">
-        <v>317</v>
+      <c r="A126" s="6" t="s">
+        <v>301</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="6" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="G126" s="6" t="s">
         <v>236</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="30">
-      <c r="A127" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="G127" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H127" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="I127" s="6" t="s">
-        <v>326</v>
+      <c r="A127" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>1061</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="6" t="s">
-        <v>729</v>
+        <v>432</v>
       </c>
       <c r="B128" s="7"/>
       <c r="C128" s="6" t="s">
-        <v>730</v>
+        <v>688</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>731</v>
+        <v>689</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>732</v>
+        <v>690</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>468</v>
+        <v>536</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>733</v>
+        <v>691</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>734</v>
+        <v>692</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="6" t="s">
-        <v>735</v>
+        <v>693</v>
       </c>
       <c r="B129" s="7"/>
       <c r="C129" s="6" t="s">
-        <v>736</v>
+        <v>694</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>737</v>
+        <v>695</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>738</v>
+        <v>696</v>
       </c>
       <c r="G129" s="6" t="s">
         <v>468</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>739</v>
+        <v>697</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="30">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="C130" s="6"/>
+        <v>699</v>
+      </c>
+      <c r="B130" s="7"/>
+      <c r="C130" s="6" t="s">
+        <v>700</v>
+      </c>
       <c r="D130" s="6" t="s">
-        <v>401</v>
+        <v>701</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>259</v>
+        <v>184</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>402</v>
+        <v>702</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>236</v>
+        <v>468</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>403</v>
+        <v>703</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9">
-      <c r="A131" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="B131" s="7"/>
-      <c r="C131" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>742</v>
-      </c>
-      <c r="E131" s="6" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="45">
+      <c r="A131" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F131" s="6" t="s">
-        <v>743</v>
-      </c>
-      <c r="G131" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="H131" s="6" t="s">
-        <v>744</v>
-      </c>
-      <c r="I131" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9">
-      <c r="A132" s="6" t="s">
-        <v>746</v>
-      </c>
-      <c r="B132" s="7"/>
-      <c r="C132" s="6" t="s">
-        <v>747</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>748</v>
-      </c>
-      <c r="E132" s="6" t="s">
+      <c r="F131" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="30">
+      <c r="A132" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="30">
+      <c r="A133" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="B133" s="7"/>
+      <c r="C133" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="E133" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F132" s="6" t="s">
-        <v>749</v>
-      </c>
-      <c r="G132" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>750</v>
-      </c>
-      <c r="I132" s="6" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="30">
-      <c r="A133" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="E133" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="F133" s="6" t="s">
-        <v>410</v>
+        <v>709</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>236</v>
+        <v>468</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="I133" s="6"/>
+        <v>710</v>
+      </c>
+      <c r="I133" s="6" t="s">
+        <v>711</v>
+      </c>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="D134" s="6"/>
+      <c r="A134" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>962</v>
+      </c>
       <c r="E134" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>412</v>
+        <v>963</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>236</v>
+        <v>844</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>413</v>
+        <v>964</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>367</v>
+        <v>965</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="30">
       <c r="A135" s="6" t="s">
-        <v>812</v>
+        <v>893</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>813</v>
+        <v>894</v>
       </c>
       <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
+      <c r="D135" s="6" t="s">
+        <v>895</v>
+      </c>
       <c r="E135" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>814</v>
+        <v>896</v>
       </c>
       <c r="G135" s="6" t="s">
-        <v>793</v>
+        <v>844</v>
       </c>
       <c r="H135" s="6" t="s">
-        <v>815</v>
+        <v>897</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>816</v>
+        <v>898</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="6" t="s">
-        <v>752</v>
+        <v>712</v>
       </c>
       <c r="B136" s="7"/>
       <c r="C136" s="6" t="s">
-        <v>753</v>
+        <v>713</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>754</v>
+        <v>714</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>755</v>
+        <v>715</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>468</v>
+        <v>536</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>756</v>
+        <v>716</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="30">
       <c r="A137" s="6" t="s">
-        <v>758</v>
-      </c>
-      <c r="B137" s="7"/>
-      <c r="C137" s="6" t="s">
-        <v>759</v>
-      </c>
+        <v>954</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="C137" s="6"/>
       <c r="D137" s="6" t="s">
-        <v>760</v>
+        <v>956</v>
       </c>
       <c r="E137" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>957</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="H137" s="6" t="s">
+        <v>958</v>
+      </c>
+      <c r="I137" s="6" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="B138" s="7"/>
+      <c r="C138" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="E138" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F137" s="6" t="s">
-        <v>761</v>
-      </c>
-      <c r="G137" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="H137" s="6" t="s">
-        <v>762</v>
-      </c>
-      <c r="I137" s="6" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" ht="30">
-      <c r="A138" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E138" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="F138" s="6" t="s">
-        <v>282</v>
+        <v>721</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>236</v>
+        <v>446</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>264</v>
+        <v>722</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>265</v>
+        <v>723</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="30">
-      <c r="A139" s="6" t="s">
-        <v>888</v>
+      <c r="A139" s="8" t="s">
+        <v>317</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>889</v>
+        <v>318</v>
       </c>
       <c r="C139" s="6"/>
       <c r="D139" s="6" t="s">
-        <v>890</v>
+        <v>319</v>
       </c>
       <c r="E139" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H139" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="I139" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="30">
+      <c r="A140" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C140" s="6"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F139" s="6" t="s">
-        <v>891</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="H139" s="6" t="s">
-        <v>892</v>
-      </c>
-      <c r="I139" s="6" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" ht="45">
-      <c r="A140" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="C140" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E140" s="6" t="s">
-        <v>184</v>
-      </c>
       <c r="F140" s="6" t="s">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="G140" s="6" t="s">
         <v>236</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>269</v>
+        <v>325</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" ht="30">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
       <c r="A141" s="6" t="s">
-        <v>764</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>765</v>
-      </c>
+        <v>724</v>
+      </c>
+      <c r="B141" s="7"/>
       <c r="C141" s="6" t="s">
-        <v>766</v>
+        <v>725</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>767</v>
+        <v>726</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>768</v>
+        <v>727</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="H141" s="6" t="s">
-        <v>769</v>
+        <v>728</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>770</v>
+        <v>729</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" s="6" t="s">
-        <v>929</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>930</v>
-      </c>
-      <c r="C142" s="6"/>
+        <v>730</v>
+      </c>
+      <c r="B142" s="7"/>
+      <c r="C142" s="6" t="s">
+        <v>731</v>
+      </c>
       <c r="D142" s="6" t="s">
-        <v>931</v>
+        <v>732</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>8</v>
+        <v>184</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>932</v>
+        <v>733</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>849</v>
+        <v>468</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>933</v>
+        <v>734</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>934</v>
+        <v>735</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="30">
-      <c r="A143" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>818</v>
-      </c>
-      <c r="C143" s="6"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>819</v>
-      </c>
-      <c r="G143" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="H143" s="6" t="s">
-        <v>820</v>
-      </c>
-      <c r="I143" s="6" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9">
-      <c r="A144" s="6" t="s">
-        <v>771</v>
-      </c>
-      <c r="B144" s="7"/>
-      <c r="C144" s="6" t="s">
-        <v>772</v>
-      </c>
-      <c r="D144" s="6" t="s">
-        <v>773</v>
-      </c>
-      <c r="E144" s="6" t="s">
+      <c r="A143" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F144" s="6" t="s">
-        <v>774</v>
-      </c>
-      <c r="G144" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="I144" s="6" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9">
+      <c r="F143" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="30">
+      <c r="A144" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="30">
       <c r="A145" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="B145" s="7"/>
-      <c r="C145" s="6" t="s">
-        <v>778</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C145" s="6"/>
       <c r="D145" s="6" t="s">
-        <v>779</v>
+        <v>401</v>
       </c>
       <c r="E145" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H145" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="I145" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="B146" s="7"/>
+      <c r="C146" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="E146" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F145" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="G145" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="H145" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="I145" s="6" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" ht="30">
-      <c r="A146" s="6" t="s">
-        <v>803</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>804</v>
-      </c>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F146" s="6" t="s">
-        <v>805</v>
+        <v>738</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>793</v>
+        <v>446</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>806</v>
+        <v>739</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>1020</v>
+        <v>740</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="6" t="s">
-        <v>433</v>
+        <v>741</v>
       </c>
       <c r="B147" s="7"/>
       <c r="C147" s="6" t="s">
-        <v>783</v>
+        <v>742</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>784</v>
+        <v>743</v>
       </c>
       <c r="E147" s="6" t="s">
         <v>184</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>785</v>
+        <v>744</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>536</v>
+        <v>446</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>786</v>
+        <v>745</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9">
-      <c r="A148" s="9" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E148" s="1" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="30">
+      <c r="A148" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="E148" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F148" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H148" s="1" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" ht="30">
-      <c r="A149" s="9" t="s">
-        <v>1042</v>
-      </c>
+      <c r="F148" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="I148" s="6"/>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="B149" s="6"/>
+      <c r="C149" s="6"/>
+      <c r="D149" s="6"/>
       <c r="E149" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F149" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H149" s="1" t="s">
-        <v>1049</v>
-      </c>
-      <c r="I149" s="1" t="s">
-        <v>1045</v>
+      <c r="F149" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="I149" s="6" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="30">
-      <c r="A150" s="1" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E150" s="1" t="s">
+      <c r="A150" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="C150" s="6"/>
+      <c r="D150" s="6"/>
+      <c r="E150" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="G150" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="I150" s="6" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="B151" s="7"/>
+      <c r="C151" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="H151" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="I151" s="6" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="B152" s="7"/>
+      <c r="C152" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="G152" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="I152" s="6" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="30">
+      <c r="A153" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C153" s="6"/>
+      <c r="D153" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="G153" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H153" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="I153" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="30">
+      <c r="A154" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>884</v>
+      </c>
+      <c r="C154" s="6"/>
+      <c r="D154" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>886</v>
+      </c>
+      <c r="G154" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="I154" s="6" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="45">
+      <c r="A155" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="G155" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H155" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="I155" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="30">
+      <c r="A156" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="I156" s="6" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" s="6" t="s">
+        <v>924</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="C157" s="6"/>
+      <c r="D157" s="6" t="s">
+        <v>926</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="G157" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="H157" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="I157" s="6" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="30">
+      <c r="A158" s="6" t="s">
+        <v>812</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="C158" s="6"/>
+      <c r="D158" s="6"/>
+      <c r="E158" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="G158" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="H158" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="I158" s="6" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="B159" s="7"/>
+      <c r="C159" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="H159" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="I159" s="6" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="B160" s="7"/>
+      <c r="C160" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="G160" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="I160" s="6" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="30">
+      <c r="A161" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>799</v>
+      </c>
+      <c r="C161" s="6"/>
+      <c r="D161" s="6"/>
+      <c r="E161" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="H161" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="I161" s="6" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B162" s="7"/>
+      <c r="C162" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="I162" s="6" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="30">
+      <c r="A163" s="10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="30">
+      <c r="A164" s="10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="30">
+      <c r="A165" s="10" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="30">
+      <c r="A166" s="10" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="45">
+      <c r="A167" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="30">
+      <c r="A168" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="30">
+      <c r="A169" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="30">
+      <c r="A170" s="10" t="s">
+        <v>866</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" s="10" t="s">
+        <v>866</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="30">
+      <c r="A172" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="30">
+      <c r="A173" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="30">
+      <c r="A174" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="30">
+      <c r="A175" s="10" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H175" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
+      <c r="A176" s="10" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="A177" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="A178" s="10" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="30">
+      <c r="A179" s="10" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
+      <c r="A180" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="A181" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="A182" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="A183" s="10" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="30">
+      <c r="A184" s="10" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="A185" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="A186" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="H186" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="I186" s="1" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="A187" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="I187" s="1" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="A188" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="H188" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="I188" s="1" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
+      <c r="A189" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H189" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
+      <c r="A190" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="A191" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="A192" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I192" s="1" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="I193" s="1" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="I194" s="1" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="30">
+      <c r="A195" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E195" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F150" s="1" t="s">
-        <v>1053</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H150" s="1" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9">
-      <c r="A151" s="1" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H151" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" ht="30">
-      <c r="A152" s="1" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E152" s="1" t="s">
+      <c r="F195" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="30">
+      <c r="A196" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="30">
+      <c r="A197" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I197" s="1" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="30">
+      <c r="A198" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="30">
+      <c r="A199" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F152" s="1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H152" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="I152" s="1" t="s">
-        <v>1066</v>
+      <c r="F199" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="I199" s="1" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="30">
+      <c r="A200" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="I200" s="1" t="s">
+        <v>1327</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J147">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J163">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E11 F146 E145:E1048576" xr:uid="{2114160C-8A15-4EA8-A16C-B04888845BCC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E11 F145 E144:E1048576" xr:uid="{2114160C-8A15-4EA8-A16C-B04888845BCC}">
       <formula1>class</formula1>
     </dataValidation>
   </dataValidations>
